--- a/fixtures/text/excel_layouts.xlsx
+++ b/fixtures/text/excel_layouts.xlsx
@@ -477,6 +477,12 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
@@ -489,6 +495,9 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -506,6 +515,16 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
@@ -543,6 +562,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A22:A32"/>
+    <mergeCell ref="A10:A21"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
